--- a/src/main/java/JavaDailyProblems.xlsx
+++ b/src/main/java/JavaDailyProblems.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Madhuri.R\OneDrive - Reliance Corporate IT Park Limited\Desktop\SDET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB847ECB-CB3A-4323-BE66-8D89F5AFAE47}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="14_{26E9A1F3-A294-4039-9F57-262EF5166CB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{9F12F7E9-0F1C-40CA-A861-3FE46DF3BBDF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="2" xr2:uid="{D56F1DA4-DD3E-41AC-A714-EA051FCB439F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="3" xr2:uid="{D56F1DA4-DD3E-41AC-A714-EA051FCB439F}"/>
   </bookViews>
   <sheets>
     <sheet name="JavaDailyProblems" sheetId="3" r:id="rId1"/>
-    <sheet name="BrowserStack20" sheetId="4" r:id="rId2"/>
-    <sheet name="progress" sheetId="5" r:id="rId3"/>
+    <sheet name="Selenium Interview Qns" sheetId="6" r:id="rId2"/>
+    <sheet name="BrowserStack20" sheetId="4" r:id="rId3"/>
+    <sheet name="progress" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="174">
   <si>
     <t>Date</t>
   </si>
@@ -289,12 +290,296 @@
   <si>
     <t>API testing using Postman</t>
   </si>
+  <si>
+    <t>How do you reverse a string in Java without using built-in methods?</t>
+  </si>
+  <si>
+    <t>How can you find the second largest number in an array without sorting it?</t>
+  </si>
+  <si>
+    <t>What is the difference between == and .equals() in Java?</t>
+  </si>
+  <si>
+    <t>How do you use the Map interface to count the frequency of characters in a string?</t>
+  </si>
+  <si>
+    <t>How do you remove duplicate elements from an ArrayList?</t>
+  </si>
+  <si>
+    <t>What is the difference between HashMap and TreeMap, and when would you use each?</t>
+  </si>
+  <si>
+    <t>How do you find the longest substring without repeating characters in a string?</t>
+  </si>
+  <si>
+    <t>How can you implement a custom sorting algorithm using Comparator?</t>
+  </si>
+  <si>
+    <t>What are the differences between ArrayList and LinkedList, and which is better for…</t>
+  </si>
+  <si>
+    <t>How do you handle exceptions in Java? Can you create a custom exception class?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maintain max1, max2 ; </t>
+  </si>
+  <si>
+    <t>Best Time to Buy and Sell Stock</t>
+  </si>
+  <si>
+    <t>Valid Anagram</t>
+  </si>
+  <si>
+    <t>Backspace String Compare</t>
+  </si>
+  <si>
+    <t>Group Anagrams</t>
+  </si>
+  <si>
+    <t>Top K Frequent Elements</t>
+  </si>
+  <si>
+    <t>Longest Substring Without Repeating Characters</t>
+  </si>
+  <si>
+    <t>Minimum Window Substring</t>
+  </si>
+  <si>
+    <t>Merge Sorted Array</t>
+  </si>
+  <si>
+    <t>Valid Parentheses</t>
+  </si>
+  <si>
+    <t>Min Stack</t>
+  </si>
+  <si>
+    <t>Rotting Oranges</t>
+  </si>
+  <si>
+    <t>Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t>House Robber</t>
+  </si>
+  <si>
+    <t>Climbing Stairs</t>
+  </si>
+  <si>
+    <t>Spiral Matrix</t>
+  </si>
+  <si>
+    <t>Merge Two Sorted Lists</t>
+  </si>
+  <si>
+    <t>Detect Cycle in a Linked List</t>
+  </si>
+  <si>
+    <t>APPLE PRACTICE</t>
+  </si>
+  <si>
+    <t>Maximum Subarray (Kadane’s)</t>
+  </si>
+  <si>
+    <t>Contains Duplicate</t>
+  </si>
+  <si>
+    <t>Product of Array Except Self</t>
+  </si>
+  <si>
+    <t>Maximum Product Subarray</t>
+  </si>
+  <si>
+    <t>Subarray Sum Equals K</t>
+  </si>
+  <si>
+    <t>Move Zeroes</t>
+  </si>
+  <si>
+    <t>Trapping Rain Water</t>
+  </si>
+  <si>
+    <t>Minimum Size Subarray Sum</t>
+  </si>
+  <si>
+    <t>Isomorphic Strings</t>
+  </si>
+  <si>
+    <t>Decode String</t>
+  </si>
+  <si>
+    <t>Happy Number</t>
+  </si>
+  <si>
+    <t>Ransom Note</t>
+  </si>
+  <si>
+    <t>Evaluate Reverse Polish Notation</t>
+  </si>
+  <si>
+    <t>Daily Temperatures</t>
+  </si>
+  <si>
+    <t>Sliding Window Maximum</t>
+  </si>
+  <si>
+    <t>Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t>Gas Station</t>
+  </si>
+  <si>
+    <t>Coin Change</t>
+  </si>
+  <si>
+    <t>Letter Combinations of a Phone Number</t>
+  </si>
+  <si>
+    <t>Maximum Depth of Binary Tree</t>
+  </si>
+  <si>
+    <t>Invert Binary Tree</t>
+  </si>
+  <si>
+    <t>Binary Tree Level Order Traversal</t>
+  </si>
+  <si>
+    <t>Validate Binary Search Tree</t>
+  </si>
+  <si>
+    <t>Stack&lt;Character&gt; s1=new Stack&lt;&gt;(); s.length(); s1.push(),pop();</t>
+  </si>
+  <si>
+    <t>Two stack, getMin: Min stack if empty or peek is more than val push else push peek</t>
+  </si>
+  <si>
+    <t>res=max=nums[0] for(1:nums.len){ max= Math.max(max+nums[i],nums[i])
+res=Math.max(res,max)
+return res;</t>
+  </si>
+  <si>
+    <t>Three Sum</t>
+  </si>
+  <si>
+    <t>nums1[i+m]=nums2[i]; Arrays.sort(nums1);</t>
+  </si>
+  <si>
+    <t>2 HashMap, h1 set value should be equal to h2 set value</t>
+  </si>
+  <si>
+    <t>Interview Qns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 1 </t>
+  </si>
+  <si>
+    <t>Part 2</t>
+  </si>
+  <si>
+    <t>Part 3</t>
+  </si>
+  <si>
+    <t>Part 4</t>
+  </si>
+  <si>
+    <t>Part 5</t>
+  </si>
+  <si>
+    <t>Part 6</t>
+  </si>
+  <si>
+    <t>Part 7</t>
+  </si>
+  <si>
+    <t>Part 8</t>
+  </si>
+  <si>
+    <t>Naveen Automation Labs' Interview Questions</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>GUIDE</t>
+  </si>
+  <si>
+    <t>Sr No.</t>
+  </si>
+  <si>
+    <t>Questions</t>
+  </si>
+  <si>
+    <t>Answers</t>
+  </si>
+  <si>
+    <t>What is Selenium, Why is it Used?</t>
+  </si>
+  <si>
+    <t>What are the components of Selenium?</t>
+  </si>
+  <si>
+    <t>What are the drawbacks of Selenium?</t>
+  </si>
+  <si>
+    <t>What are the version of Selenium? Current Version?</t>
+  </si>
+  <si>
+    <t>What is the JSON Wire Protocol, wrt to Selenium?</t>
+  </si>
+  <si>
+    <t>Explain the Selenium Architecture?</t>
+  </si>
+  <si>
+    <t>What is Hub and Node in Selenium Grid?</t>
+  </si>
+  <si>
+    <t>What is Selense in Selenium IDE?</t>
+  </si>
+  <si>
+    <t>What is Selenium Grid Extras?</t>
+  </si>
+  <si>
+    <t>What is maxInstances and MaxSessions in Selnium Grid?</t>
+  </si>
+  <si>
+    <t>What are Different types of locators?</t>
+  </si>
+  <si>
+    <t>Which to use, Xpath,Id,Name , CSS Selector?</t>
+  </si>
+  <si>
+    <t>CSS Selector is faster than Xpath</t>
+  </si>
+  <si>
+    <t>What is Xpath, how does it work?</t>
+  </si>
+  <si>
+    <t>How to reach parent of xpath?</t>
+  </si>
+  <si>
+    <t>//a[@id='hi']/.. - {/.. : is for parent}</t>
+  </si>
+  <si>
+    <t>24.09.2025</t>
+  </si>
+  <si>
+    <t>https://github.com/naveenanimation20/SeleniumInterviewQuestions</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=aFlAXLSHbCg</t>
+  </si>
+  <si>
+    <t>Cucumber Framweork</t>
+  </si>
+  <si>
+    <t>26.09.2025</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -323,8 +608,37 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF242424"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,6 +654,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -511,11 +831,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -558,6 +879,51 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -594,10 +960,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
   </cellStyles>
@@ -922,20 +1290,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="27"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="48"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -949,7 +1317,7 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="49" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -960,7 +1328,7 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="31"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="17" t="s">
         <v>13</v>
       </c>
@@ -969,7 +1337,7 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="49" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="16" t="s">
@@ -980,7 +1348,7 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
+      <c r="B9" s="51"/>
       <c r="C9" s="18" t="s">
         <v>15</v>
       </c>
@@ -989,7 +1357,7 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="18" t="s">
         <v>16</v>
       </c>
@@ -998,7 +1366,7 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="32"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="18" t="s">
         <v>17</v>
       </c>
@@ -1007,7 +1375,7 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="31"/>
+      <c r="B12" s="50"/>
       <c r="C12" s="17" t="s">
         <v>18</v>
       </c>
@@ -1023,7 +1391,7 @@
       <c r="D13" s="21"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="52" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="16" t="s">
@@ -1034,7 +1402,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="34"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="18" t="s">
         <v>21</v>
       </c>
@@ -1043,14 +1411,14 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="34"/>
+      <c r="B16" s="53"/>
       <c r="C16" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="34"/>
+      <c r="B17" s="53"/>
       <c r="C17" s="18" t="s">
         <v>23</v>
       </c>
@@ -1059,7 +1427,7 @@
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="35"/>
+      <c r="B18" s="54"/>
       <c r="C18" s="17" t="s">
         <v>24</v>
       </c>
@@ -2149,203 +2517,719 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABAFE51-CFDD-49FD-B9AD-1F203AED3998}">
-  <dimension ref="B2:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE84801-BA5E-4F91-B6C8-C0F6728754A9}">
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="3" width="41.5703125" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" customWidth="1"/>
+    <col min="2" max="2" width="52.5703125" customWidth="1"/>
+    <col min="3" max="3" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C2" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
-    </row>
-    <row r="5" spans="2:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
       <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C12" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>164</v>
+      </c>
       <c r="C13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>167</v>
+      </c>
       <c r="C15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C16" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C2:G3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8834F34A-1CE9-492C-9901-2A70BA9B2B20}">
-  <dimension ref="D3:D10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABAFE51-CFDD-49FD-B9AD-1F203AED3998}">
+  <dimension ref="B2:G78"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="44.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D3" s="37" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C2" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="45"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+    </row>
+    <row r="5" spans="2:7" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="37" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C7" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C8" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C9" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C10" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C11" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C12" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C13" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C14" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C15" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C16" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C17" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="26" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4" s="26" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="26" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="3:4" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C28" s="26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C29" s="26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C30" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C31" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C32" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C33" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C34" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C36" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="55"/>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C37" s="33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C38" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="29" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C40" s="34" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C44" s="31" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C45" s="31" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C46" s="31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C47" s="35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C50" s="39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C51" s="31" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C52" s="31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C53" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C54" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C55" s="31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C56" s="31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C57" s="31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C58" s="30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C59" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C60" s="29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C61" s="31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C62" s="31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C63" s="31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C64" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C65" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C66" s="32" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C67" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C68" s="31" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="C69" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C70" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C71" s="31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C72" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C73" s="31" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C74" s="31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C75" s="31" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C76" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C77" s="31" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C78" s="31" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:G3"/>
+    <mergeCell ref="C36:D36"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8834F34A-1CE9-492C-9901-2A70BA9B2B20}">
+  <dimension ref="D2:H16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" customWidth="1"/>
+    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="4:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="25" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D4" s="37" t="s">
+      <c r="F3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D4" s="25" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="5" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D5" t="s">
+      <c r="F4" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D5" s="25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D6" t="s">
+      <c r="F5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D6" s="25" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D7" t="s">
+      <c r="F6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D7" s="40" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="10" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D10" t="s">
         <v>79</v>
       </c>
+      <c r="F10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="4:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="F14" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D16" s="42"/>
+      <c r="E16" s="41"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{F927AF27-B465-4809-B49C-6E1A38530572}"/>
+    <hyperlink ref="G14" r:id="rId2" xr:uid="{1396D7D2-1AB4-4FC3-BFF0-0CB87D5E6608}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010093D215910041EE46A205026926E3B56E" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b73b6011550921ae70f49bc2ee80ef25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xmlns:ns4="376f05cc-017a-41da-a922-00fd3d15c307" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f90110de6f945d9f92ab4f55d0f4e60" ns3:_="" ns4:_="">
     <xsd:import namespace="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
@@ -2572,24 +3456,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B2FDDC-A607-4B97-811A-2C87CF880C14}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D1EE24-5716-4976-BD2C-B015EDF1B4E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E28685A-C42A-4306-A520-3D6CF3A07373}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2606,29 +3498,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D1EE24-5716-4976-BD2C-B015EDF1B4E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B2FDDC-A607-4B97-811A-2C87CF880C14}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/main/java/JavaDailyProblems.xlsx
+++ b/src/main/java/JavaDailyProblems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Madhuri.R\OneDrive - Reliance Corporate IT Park Limited\Desktop\SDET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="14_{26E9A1F3-A294-4039-9F57-262EF5166CB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{9F12F7E9-0F1C-40CA-A861-3FE46DF3BBDF}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="14_{26E9A1F3-A294-4039-9F57-262EF5166CB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{970323B8-B06F-4683-B6BD-3AB36E3DC3FB}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="3" xr2:uid="{D56F1DA4-DD3E-41AC-A714-EA051FCB439F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="195">
   <si>
     <t>Date</t>
   </si>
@@ -574,12 +574,267 @@
   <si>
     <t>26.09.2025</t>
   </si>
+  <si>
+    <t>HM Round</t>
+  </si>
+  <si>
+    <t>1. Behavioral &amp; Situational Questions</t>
+  </si>
+  <si>
+    <t>Tell me about a time you found a critical bug late in the cycle. What did you do?</t>
+  </si>
+  <si>
+    <t>Describe a conflict you had with a developer. How did you resolve it?</t>
+  </si>
+  <si>
+    <t>Have you ever disagreed with a product requirement? What did you do?</t>
+  </si>
+  <si>
+    <t>How do you prioritize tasks when you're assigned multiple testing responsibilities?</t>
+  </si>
+  <si>
+    <t>2.Project &amp; Experience Discussion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Your </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>automation frameworks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Selenium, Playwright, Cypress, etc.).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CI/CD pipelines</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and how you integrated tests.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>test strategy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> you defined or contributed to.</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Technical Depth (at a High Level)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Your </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>understanding of testing principles</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>: unit, integration, end-to-end.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">How you </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>design test cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, especially for edge cases.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Knowledge of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>test pyramid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>shift-left testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>code coverage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, etc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experience with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>bug tracking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>test management</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>version control</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tools.</t>
+    </r>
+  </si>
+  <si>
+    <t>4.Test Design &amp; Quality Strategy</t>
+  </si>
+  <si>
+    <t>How would you test a login system?</t>
+  </si>
+  <si>
+    <t>How do you ensure your test suite is maintainable?</t>
+  </si>
+  <si>
+    <t>What’s your approach to flaky tests?</t>
+  </si>
+  <si>
+    <t>How do you measure quality in your releases?</t>
+  </si>
+  <si>
+    <t>5.Team Fit &amp; Communication</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -636,6 +891,12 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -836,7 +1097,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -962,6 +1223,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3091,7 +3359,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8834F34A-1CE9-492C-9901-2A70BA9B2B20}">
-  <dimension ref="D2:H16"/>
+  <dimension ref="D2:H50"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
@@ -3201,6 +3469,117 @@
     <row r="16" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D16" s="42"/>
       <c r="E16" s="41"/>
+    </row>
+    <row r="18" spans="4:4" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="D18" s="57" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D19" s="56" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D20" s="58" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D21" s="58" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D22" s="58" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D23" s="58" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D24" s="26"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D25" s="26"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D28" s="56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D29" s="58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D30" s="56" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D31" s="31" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D35" s="56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D36" s="58" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D37" s="58" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D38" s="58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" spans="4:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="D39" s="58" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="43" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D43" s="56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D44" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="45" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D45" s="31" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="46" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D46" s="31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D47" s="31" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D50" s="56" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3221,15 +3600,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010093D215910041EE46A205026926E3B56E" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b73b6011550921ae70f49bc2ee80ef25">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="a6e5cf0a-2090-4fbc-90f6-bd2e05553039" xmlns:ns4="376f05cc-017a-41da-a922-00fd3d15c307" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5f90110de6f945d9f92ab4f55d0f4e60" ns3:_="" ns4:_="">
     <xsd:import namespace="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
@@ -3456,32 +3826,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11B2FDDC-A607-4B97-811A-2C87CF880C14}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
     <ds:schemaRef ds:uri="a6e5cf0a-2090-4fbc-90f6-bd2e05553039"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="376f05cc-017a-41da-a922-00fd3d15c307"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D1EE24-5716-4976-BD2C-B015EDF1B4E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E28685A-C42A-4306-A520-3D6CF3A07373}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3498,4 +3869,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1D1EE24-5716-4976-BD2C-B015EDF1B4E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>